--- a/4- CATEGORÍAS Y OPCIONES BACKEND/4- CATEGORÍAS Y OPCIONES BACKEND.xlsx
+++ b/4- CATEGORÍAS Y OPCIONES BACKEND/4- CATEGORÍAS Y OPCIONES BACKEND.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\4- CATEGORÍAS Y OPCIONES BACKEND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8563FC51-966D-4BEE-A877-B38ABEEB5D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81213320-C052-41DA-96AE-7B17E1381895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{06520589-45E0-4B9A-A076-7CF20A3C8CDB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
   <si>
     <t>ESTADO DE LAS SOLICITUDES</t>
   </si>
@@ -45,60 +45,18 @@
     <t>N°</t>
   </si>
   <si>
-    <t>RECHAZADA POR SERVICIO/UNIDAD</t>
-  </si>
-  <si>
-    <t>INGRESADA POR ADMINISTRADOR DE PASANTÍAS</t>
-  </si>
-  <si>
-    <t>SERVICIO/UNIDAD INDICA MODIFICACIÓN DE PERIODO Y/O DE HORAS</t>
-  </si>
-  <si>
-    <t>APROBADA POR SERVICIO/UNIDAD</t>
-  </si>
-  <si>
-    <t>EN GESTIÓN DE LOS DOCUMENTOS OBLIGATORIOS</t>
-  </si>
-  <si>
-    <t>EN ELABORACIÓN DE LA RESOLUCIÓN EXENTA</t>
-  </si>
-  <si>
-    <t>EN REVISIÓN POR SERVICIO/UNIDAD</t>
-  </si>
-  <si>
-    <t>EN ACTIVACIÓN DE QR PARA CONTROL DE ACCESOS</t>
-  </si>
-  <si>
     <t>AUTORIZADA POR RESOLUCIÓN EXENTA</t>
   </si>
   <si>
     <t>RECHAZADA POR RESOLUCIÓN EXENTA</t>
   </si>
   <si>
-    <t>PERIODO PASANTÍA</t>
-  </si>
-  <si>
-    <t>NUEVA PROPUESTA DE FECHA(S) Y/U HORA(S) POR SERVICIO/UNIDAD</t>
-  </si>
-  <si>
     <t>MOTIVO DEL RECHAZO DE UNA SOLICITUD</t>
   </si>
   <si>
-    <t>NO FACTIBILIDAD DEL SERVICIO/UNIDAD</t>
-  </si>
-  <si>
-    <t>DOCUMENTACIÓN INCOMPLETA</t>
-  </si>
-  <si>
-    <t>NO ACEPTACIÓN DE CONTRA PROPUESTA</t>
-  </si>
-  <si>
     <t>OTROS</t>
   </si>
   <si>
-    <t>PROPUESTA DE FECHA(S) Y/U HORA(S) POR SERVICIO/UNIDAD</t>
-  </si>
-  <si>
     <t>REQUIERE INSTITUCIÓN DE ORIGEN</t>
   </si>
   <si>
@@ -141,12 +99,6 @@
     <t xml:space="preserve">PENDIENTE DE NOTIFICACIÓN </t>
   </si>
   <si>
-    <t>NOTIFICACIÓN A JEFATURA Y  SECRETARIA PARA REVISIÓN DE FACTIBILIDAD</t>
-  </si>
-  <si>
-    <t>NOTIFICACIÓN A JEFATURA, SECRETARIA, SOLICITANTE E INSTITUCIÓN SOBRE DECISIÓN DE LA SOLICITUD</t>
-  </si>
-  <si>
     <t>NOTIFICACIÓN A GESTOR DE QR PARA ACTIVACIÓN</t>
   </si>
   <si>
@@ -250,6 +202,72 @@
   </si>
   <si>
     <t>E: FORMULARIO SOLICITUD DE PASANTIA DE PERFECCIONAMIENTO PARA PROFESIONALES Y TÉCNICOS DE OTRAS CARRERAS, Y ADMINISTRATIVOS DE FORMA PARTICULAR EN EL HOSPITAL SAN JUAN DE DIOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARTA SOLICITUD </t>
+  </si>
+  <si>
+    <t>GUARDADA COMO BORRADOR</t>
+  </si>
+  <si>
+    <t>INGRESADA</t>
+  </si>
+  <si>
+    <t>DOCUMENTACIÓN NO CUMPLE CON LO EXIGIDO</t>
+  </si>
+  <si>
+    <t>NO EXISTE FACTIBILIDAD POR EL SERVICIO CLÍNICO</t>
+  </si>
+  <si>
+    <t>NO ACEPTACIÓN POR SOLICITANTE DE CONTRA PROPUESTA DE FECHAS Y/U HORAS</t>
+  </si>
+  <si>
+    <t>NOTIFICACIÓN A JEFATURA, SECRETARIA, SOLICITANTE SOBRE RECHAZO DE LA SOLICITUD DE PASANTÍA</t>
+  </si>
+  <si>
+    <t>NOTIFICACIÓN A JEFATURA, SECRETARIA, SOLICITANTE E INSTITUCIÓN SOBRE AUTORIZACIÓN DE PASANTÍA</t>
+  </si>
+  <si>
+    <t>ESTADO DE LA PASANTÍA</t>
+  </si>
+  <si>
+    <t>POR INICIAR</t>
+  </si>
+  <si>
+    <t>EN PERIODO</t>
+  </si>
+  <si>
+    <t>FINALIZADA</t>
+  </si>
+  <si>
+    <t>DESISTIDA</t>
+  </si>
+  <si>
+    <t>CREDENCIAL</t>
+  </si>
+  <si>
+    <t>SIN RETIRAR</t>
+  </si>
+  <si>
+    <t>RETIRADA</t>
+  </si>
+  <si>
+    <t>SIN DEVOLVER</t>
+  </si>
+  <si>
+    <t>DEVUELTA</t>
+  </si>
+  <si>
+    <t>ESTADO DE QR</t>
+  </si>
+  <si>
+    <t>POR ACTIVAR</t>
+  </si>
+  <si>
+    <t>ACTIVADO</t>
+  </si>
+  <si>
+    <t>DESACTIVADO</t>
   </si>
 </sst>
 </file>
@@ -615,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC36414A-BB0E-45D3-BC24-510E45F66888}">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" bestFit="1" customWidth="1"/>
@@ -636,7 +654,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -644,13 +662,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -658,13 +676,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -672,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -686,227 +704,233 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
       <c r="E8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>50</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
       <c r="E12">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>19</v>
-      </c>
       <c r="E15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23">
-        <v>3</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -914,427 +938,424 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>49</v>
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E30">
         <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E36">
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
       <c r="E37">
         <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E38">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>48</v>
+      <c r="A40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>35</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50">
+        <v>4</v>
+      </c>
+      <c r="F50" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>6</v>
+      </c>
+      <c r="B55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="F55" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60">
         <v>7</v>
       </c>
-      <c r="B46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>8</v>
-      </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>9</v>
-      </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>10</v>
-      </c>
-      <c r="B49" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>2</v>
-      </c>
-      <c r="B54" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>3</v>
-      </c>
-      <c r="B55" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="F60" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
         <v>4</v>
       </c>
-      <c r="B56" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="B62" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
         <v>5</v>
       </c>
-      <c r="B57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="B63" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
         <v>6</v>
       </c>
-      <c r="B58" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>1</v>
-      </c>
-      <c r="B62" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>3</v>
-      </c>
       <c r="B64" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>5</v>
-      </c>
-      <c r="B66" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>6</v>
-      </c>
-      <c r="B67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>1</v>
-      </c>
-      <c r="B71" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>2</v>
-      </c>
-      <c r="B72" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>3</v>
-      </c>
-      <c r="B73" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>4</v>
-      </c>
-      <c r="B74" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>5</v>
-      </c>
-      <c r="B75" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>6</v>
-      </c>
-      <c r="B76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>7</v>
-      </c>
-      <c r="B77" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
